--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5EA934-3AA2-45A8-9591-823FD097A89C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E9B35F-C857-43B4-9603-B45B0F11409A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4671" uniqueCount="4470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4686" uniqueCount="4485">
   <si>
     <t>大正新脩大藏經</t>
   </si>
@@ -13623,6 +13623,76 @@
   </si>
   <si>
     <t>X0714 四分律含注戒本疏行宗記 (4卷)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>演培法師全集</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>YPa001 演培</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Noto Sans TC"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>⻑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>老傳略</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YPa002 出版緣起</t>
+  </si>
+  <si>
+    <t>YPa003 序文</t>
+  </si>
+  <si>
+    <t>經釋篇</t>
+  </si>
+  <si>
+    <t>YP0001 ⾦剛般若波羅密經講記</t>
+  </si>
+  <si>
+    <t>YP0002 ⾦剛經概要</t>
+  </si>
+  <si>
+    <t>YP0003 ⾦光明經空品講記</t>
+  </si>
+  <si>
+    <t>YP0004 般若波羅密多⼼經講記</t>
+  </si>
+  <si>
+    <t>YP0005 般若波羅密多⼼經講記</t>
+  </si>
+  <si>
+    <t>YP0006 ⼼經⼗⼆講</t>
+  </si>
+  <si>
+    <t>YP0007 佛說⼗善業道經講記</t>
+  </si>
+  <si>
+    <t>YP0008 佛說八⼤⼈覺經講記</t>
+  </si>
+  <si>
+    <t>YP0009 ⼤寶積妙慧童女經講記</t>
+  </si>
+  <si>
+    <t>YP0010 勝鬘師子吼一乘大方便方廣經講記</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
@@ -13630,7 +13700,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -13807,6 +13877,12 @@
       <sz val="12"/>
       <name val="細明體"/>
       <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Noto Sans TC"/>
+      <family val="2"/>
       <charset val="136"/>
     </font>
   </fonts>
@@ -14590,7 +14666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4671"/>
+  <dimension ref="A1:F4686"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -37985,36 +38061,125 @@
     </row>
     <row r="4665" spans="2:4">
       <c r="B4665" t="s">
-        <v>4435</v>
-      </c>
-    </row>
-    <row r="4666" spans="2:4">
-      <c r="C4666" s="1" t="s">
-        <v>4436</v>
-      </c>
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="4666" spans="2:4" ht="19.8">
+      <c r="C4666" t="s">
+        <v>4471</v>
+      </c>
+      <c r="D4666" s="1"/>
     </row>
     <row r="4667" spans="2:4">
       <c r="C4667" s="1" t="s">
+        <v>4472</v>
+      </c>
+      <c r="D4667" s="1"/>
+    </row>
+    <row r="4668" spans="2:4">
+      <c r="C4668" s="1" t="s">
+        <v>4473</v>
+      </c>
+      <c r="D4668" s="1"/>
+    </row>
+    <row r="4669" spans="2:4">
+      <c r="C4669" s="1" t="s">
+        <v>4474</v>
+      </c>
+      <c r="D4669" s="1"/>
+    </row>
+    <row r="4670" spans="2:4" s="1" customFormat="1">
+      <c r="D4670" s="1" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="4671" spans="2:4" s="1" customFormat="1">
+      <c r="D4671" s="1" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="4672" spans="2:4" s="1" customFormat="1">
+      <c r="D4672" s="1" t="s">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="4673" spans="2:4">
+      <c r="C4673" s="1"/>
+      <c r="D4673" s="1" t="s">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="4674" spans="2:4">
+      <c r="C4674" s="1"/>
+      <c r="D4674" s="1" t="s">
+        <v>4479</v>
+      </c>
+    </row>
+    <row r="4675" spans="2:4">
+      <c r="C4675" s="1"/>
+      <c r="D4675" s="1" t="s">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="4676" spans="2:4">
+      <c r="C4676" s="1"/>
+      <c r="D4676" s="1" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="4677" spans="2:4">
+      <c r="C4677" s="1"/>
+      <c r="D4677" s="1" t="s">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="4678" spans="2:4">
+      <c r="C4678" s="1"/>
+      <c r="D4678" s="1" t="s">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="4679" spans="2:4">
+      <c r="C4679" s="1"/>
+      <c r="D4679" s="1" t="s">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="4680" spans="2:4">
+      <c r="B4680" t="s">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="4681" spans="2:4">
+      <c r="C4681" s="1" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="4682" spans="2:4">
+      <c r="C4682" s="1" t="s">
         <v>4440</v>
       </c>
     </row>
-    <row r="4668" spans="2:4" s="1" customFormat="1">
-      <c r="C4668" s="1" t="s">
+    <row r="4683" spans="2:4">
+      <c r="B4683" s="1"/>
+      <c r="C4683" s="1" t="s">
         <v>4444</v>
       </c>
     </row>
-    <row r="4669" spans="2:4" s="1" customFormat="1">
-      <c r="C4669" s="1" t="s">
+    <row r="4684" spans="2:4">
+      <c r="B4684" s="1"/>
+      <c r="C4684" s="1" t="s">
         <v>4445</v>
       </c>
     </row>
-    <row r="4670" spans="2:4" s="1" customFormat="1">
-      <c r="C4670" s="1" t="s">
+    <row r="4685" spans="2:4">
+      <c r="B4685" s="1"/>
+      <c r="C4685" s="1" t="s">
         <v>4446</v>
       </c>
     </row>
-    <row r="4671" spans="2:4">
-      <c r="C4671" s="1" t="s">
+    <row r="4686" spans="2:4">
+      <c r="C4686" s="1" t="s">
         <v>4448</v>
       </c>
     </row>

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65E9B35F-C857-43B4-9603-B45B0F11409A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3090F3C7-3891-41A2-AAED-98331E36CDBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12252" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="simple" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4686" uniqueCount="4485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4699" uniqueCount="4498">
   <si>
     <t>大正新脩大藏經</t>
   </si>
@@ -13695,12 +13695,61 @@
     <t>YP0010 勝鬘師子吼一乘大方便方廣經講記</t>
     <phoneticPr fontId="18" type="noConversion"/>
   </si>
+  <si>
+    <t>YP0011 維摩詰所說經講記（上）（下）(第1卷-第6卷)(第7卷-第6卷)</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0012 解深密經語體釋</t>
+    <phoneticPr fontId="23" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0014 華嚴經普賢行願品講記</t>
+  </si>
+  <si>
+    <t>YP0013 佛說彌勒大成佛經講記</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0015 觀世音菩薩普門品講記</t>
+  </si>
+  <si>
+    <t>YP0016 藥師經講記</t>
+  </si>
+  <si>
+    <t>YP0017 六祖壇經講記</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0018 梵網經菩薩戒本講記</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>律釋篇</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0019 毘尼日用切要講記</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0020 八關齋戒十講</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>論釋篇</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0021 異部宗輪論語體釋</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -13884,6 +13933,20 @@
       <name val="Noto Sans TC"/>
       <family val="2"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -14311,7 +14374,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -14319,6 +14382,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -14666,7 +14732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4686"/>
+  <dimension ref="A1:F4699"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -38103,83 +38169,159 @@
         <v>4477</v>
       </c>
     </row>
-    <row r="4673" spans="2:4">
+    <row r="4673" spans="3:4">
       <c r="C4673" s="1"/>
       <c r="D4673" s="1" t="s">
         <v>4478</v>
       </c>
     </row>
-    <row r="4674" spans="2:4">
+    <row r="4674" spans="3:4">
       <c r="C4674" s="1"/>
       <c r="D4674" s="1" t="s">
         <v>4479</v>
       </c>
     </row>
-    <row r="4675" spans="2:4">
+    <row r="4675" spans="3:4">
       <c r="C4675" s="1"/>
       <c r="D4675" s="1" t="s">
         <v>4480</v>
       </c>
     </row>
-    <row r="4676" spans="2:4">
+    <row r="4676" spans="3:4">
       <c r="C4676" s="1"/>
       <c r="D4676" s="1" t="s">
         <v>4481</v>
       </c>
     </row>
-    <row r="4677" spans="2:4">
+    <row r="4677" spans="3:4">
       <c r="C4677" s="1"/>
       <c r="D4677" s="1" t="s">
         <v>4482</v>
       </c>
     </row>
-    <row r="4678" spans="2:4">
+    <row r="4678" spans="3:4">
       <c r="C4678" s="1"/>
       <c r="D4678" s="1" t="s">
         <v>4483</v>
       </c>
     </row>
-    <row r="4679" spans="2:4">
+    <row r="4679" spans="3:4">
       <c r="C4679" s="1"/>
       <c r="D4679" s="1" t="s">
         <v>4484</v>
       </c>
     </row>
-    <row r="4680" spans="2:4">
-      <c r="B4680" t="s">
+    <row r="4680" spans="3:4">
+      <c r="C4680" s="1"/>
+      <c r="D4680" s="1" t="s">
+        <v>4485</v>
+      </c>
+    </row>
+    <row r="4681" spans="3:4">
+      <c r="C4681" s="1"/>
+      <c r="D4681" s="1" t="s">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="4682" spans="3:4">
+      <c r="C4682" s="1"/>
+      <c r="D4682" s="1" t="s">
+        <v>4488</v>
+      </c>
+    </row>
+    <row r="4683" spans="3:4">
+      <c r="C4683" s="1"/>
+      <c r="D4683" s="3" t="s">
+        <v>4487</v>
+      </c>
+    </row>
+    <row r="4684" spans="3:4">
+      <c r="C4684" s="1"/>
+      <c r="D4684" s="3" t="s">
+        <v>4489</v>
+      </c>
+    </row>
+    <row r="4685" spans="3:4">
+      <c r="C4685" s="1"/>
+      <c r="D4685" s="3" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="4686" spans="3:4">
+      <c r="C4686" s="1"/>
+      <c r="D4686" t="s">
+        <v>4491</v>
+      </c>
+    </row>
+    <row r="4687" spans="3:4">
+      <c r="C4687" s="1" t="s">
+        <v>4493</v>
+      </c>
+    </row>
+    <row r="4688" spans="3:4">
+      <c r="C4688" s="1"/>
+      <c r="D4688" t="s">
+        <v>4492</v>
+      </c>
+    </row>
+    <row r="4689" spans="2:4">
+      <c r="C4689" s="1"/>
+      <c r="D4689" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="4690" spans="2:4">
+      <c r="C4690" s="1"/>
+      <c r="D4690" t="s">
+        <v>4495</v>
+      </c>
+    </row>
+    <row r="4691" spans="2:4">
+      <c r="C4691" s="1" t="s">
+        <v>4496</v>
+      </c>
+    </row>
+    <row r="4692" spans="2:4">
+      <c r="C4692" s="1"/>
+      <c r="D4692" s="1" t="s">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="4693" spans="2:4">
+      <c r="B4693" t="s">
         <v>4435</v>
       </c>
     </row>
-    <row r="4681" spans="2:4">
-      <c r="C4681" s="1" t="s">
+    <row r="4694" spans="2:4">
+      <c r="C4694" s="1" t="s">
         <v>4436</v>
       </c>
     </row>
-    <row r="4682" spans="2:4">
-      <c r="C4682" s="1" t="s">
+    <row r="4695" spans="2:4">
+      <c r="C4695" s="1" t="s">
         <v>4440</v>
       </c>
     </row>
-    <row r="4683" spans="2:4">
-      <c r="B4683" s="1"/>
-      <c r="C4683" s="1" t="s">
+    <row r="4696" spans="2:4">
+      <c r="B4696" s="1"/>
+      <c r="C4696" s="1" t="s">
         <v>4444</v>
       </c>
     </row>
-    <row r="4684" spans="2:4">
-      <c r="B4684" s="1"/>
-      <c r="C4684" s="1" t="s">
+    <row r="4697" spans="2:4">
+      <c r="B4697" s="1"/>
+      <c r="C4697" s="1" t="s">
         <v>4445</v>
       </c>
     </row>
-    <row r="4685" spans="2:4">
-      <c r="B4685" s="1"/>
-      <c r="C4685" s="1" t="s">
+    <row r="4698" spans="2:4">
+      <c r="B4698" s="1"/>
+      <c r="C4698" s="1" t="s">
         <v>4446</v>
       </c>
     </row>
-    <row r="4686" spans="2:4">
-      <c r="C4686" s="1" t="s">
+    <row r="4699" spans="2:4">
+      <c r="C4699" s="1" t="s">
         <v>4448</v>
       </c>
     </row>

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536968BC-337F-42AE-9C0E-1B086AC80BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF417339-4A86-4D50-8C16-BF3E12F93C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="new-simple-2026.R2" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14112" uniqueCount="4531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14108" uniqueCount="4546">
   <si>
     <t>大正新脩大藏經</t>
   </si>
@@ -13849,6 +13849,65 @@
   </si>
   <si>
     <t>T2865..T2920</t>
+  </si>
+  <si>
+    <t>YP0027 慈悲三昧水懺講記</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>YP0028 勸發菩提心文講記</t>
+  </si>
+  <si>
+    <t>YP0029 成佛之道偈頌講記</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>B0134 闢邪集</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>B0130 靈峰宗論</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_019..021 JB277 (卷19-21) 雲棲法彙（選錄）雲棲大師遺稿</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_025 JB277 (卷25) 雲棲法彙（選錄）雲棲大師塔銘</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_023 JB277 (卷23) 雲棲法彙（選錄）雲棲紀事</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_012 JB277 (卷12) 雲棲法彙（選錄）竹窗隨筆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_013 JB277 (卷13) 雲棲法彙（選錄）竹窗二筆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_014 JB277 (卷14) 雲棲法彙（選錄）竹窗三筆</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_015 JB277 (卷15) 雲棲法彙（選錄）正訛集</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_022 JB277 (卷22) 雲棲法彙（選錄）雲棲共住規約</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_016 JB277 (卷16) 雲棲法彙（選錄）直道錄</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>JB277_017..018 JB277 (卷17-18) 雲棲法彙（選錄）山房雜錄</t>
+    <phoneticPr fontId="20" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -14838,7 +14897,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C640C8-AF4E-454A-93BC-513EE82F584A}">
-  <dimension ref="A1:F4704"/>
+  <dimension ref="A1:F4700"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -37133,7 +37192,7 @@
     </row>
     <row r="4449" spans="4:5">
       <c r="E4449" t="s">
-        <v>3999</v>
+        <v>4536</v>
       </c>
     </row>
     <row r="4450" spans="4:5">
@@ -37143,7 +37202,7 @@
     </row>
     <row r="4451" spans="4:5">
       <c r="E4451" t="s">
-        <v>4001</v>
+        <v>4537</v>
       </c>
     </row>
     <row r="4452" spans="4:5">
@@ -37153,7 +37212,7 @@
     </row>
     <row r="4453" spans="4:5">
       <c r="E4453" t="s">
-        <v>4003</v>
+        <v>4538</v>
       </c>
     </row>
     <row r="4454" spans="4:5">
@@ -37163,7 +37222,7 @@
     </row>
     <row r="4455" spans="4:5">
       <c r="E4455" t="s">
-        <v>4005</v>
+        <v>4539</v>
       </c>
     </row>
     <row r="4456" spans="4:5">
@@ -37173,7 +37232,7 @@
     </row>
     <row r="4457" spans="4:5">
       <c r="E4457" t="s">
-        <v>4007</v>
+        <v>4540</v>
       </c>
     </row>
     <row r="4458" spans="4:5">
@@ -37183,7 +37242,7 @@
     </row>
     <row r="4459" spans="4:5">
       <c r="E4459" t="s">
-        <v>4009</v>
+        <v>4541</v>
       </c>
     </row>
     <row r="4460" spans="4:5">
@@ -37193,7 +37252,7 @@
     </row>
     <row r="4461" spans="4:5">
       <c r="E4461" t="s">
-        <v>4011</v>
+        <v>4542</v>
       </c>
     </row>
     <row r="4462" spans="4:5">
@@ -37203,7 +37262,7 @@
     </row>
     <row r="4463" spans="4:5">
       <c r="E4463" t="s">
-        <v>4013</v>
+        <v>4543</v>
       </c>
     </row>
     <row r="4464" spans="4:5">
@@ -37213,7 +37272,7 @@
     </row>
     <row r="4465" spans="3:5">
       <c r="E4465" t="s">
-        <v>4015</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="4466" spans="3:5">
@@ -37223,1235 +37282,1215 @@
     </row>
     <row r="4467" spans="3:5">
       <c r="E4467" t="s">
-        <v>4017</v>
+        <v>4545</v>
       </c>
     </row>
     <row r="4468" spans="3:5">
       <c r="D4468" t="s">
-        <v>4018</v>
+        <v>4535</v>
       </c>
     </row>
     <row r="4469" spans="3:5">
-      <c r="E4469" t="s">
-        <v>3191</v>
+      <c r="C4469" t="s">
+        <v>2861</v>
       </c>
     </row>
     <row r="4470" spans="3:5">
-      <c r="E4470" t="s">
-        <v>2826</v>
+      <c r="D4470" t="s">
+        <v>4417</v>
       </c>
     </row>
     <row r="4471" spans="3:5">
-      <c r="E4471" t="s">
-        <v>2825</v>
+      <c r="D4471" t="s">
+        <v>4176</v>
       </c>
     </row>
     <row r="4472" spans="3:5">
-      <c r="E4472" t="s">
-        <v>4019</v>
+      <c r="D4472" t="s">
+        <v>4177</v>
       </c>
     </row>
     <row r="4473" spans="3:5">
-      <c r="C4473" t="s">
-        <v>2861</v>
+      <c r="D4473" t="s">
+        <v>4178</v>
       </c>
     </row>
     <row r="4474" spans="3:5">
       <c r="D4474" t="s">
-        <v>4417</v>
+        <v>4534</v>
       </c>
     </row>
     <row r="4475" spans="3:5">
       <c r="D4475" t="s">
-        <v>4176</v>
+        <v>4179</v>
       </c>
     </row>
     <row r="4476" spans="3:5">
       <c r="D4476" t="s">
-        <v>4177</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="4477" spans="3:5">
       <c r="D4477" t="s">
-        <v>4178</v>
+        <v>4181</v>
       </c>
     </row>
     <row r="4478" spans="3:5">
       <c r="D4478" t="s">
-        <v>4020</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="4479" spans="3:5">
       <c r="E4479" t="s">
-        <v>2826</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="4480" spans="3:5">
-      <c r="E4480" t="s">
-        <v>4021</v>
+      <c r="D4480" t="s">
+        <v>4183</v>
       </c>
     </row>
     <row r="4481" spans="3:5">
-      <c r="E4481" t="s">
-        <v>4022</v>
+      <c r="D4481" t="s">
+        <v>4184</v>
       </c>
     </row>
     <row r="4482" spans="3:5">
       <c r="D4482" t="s">
-        <v>4179</v>
+        <v>4185</v>
       </c>
     </row>
     <row r="4483" spans="3:5">
-      <c r="D4483" t="s">
-        <v>4180</v>
+      <c r="C4483" t="s">
+        <v>2893</v>
       </c>
     </row>
     <row r="4484" spans="3:5">
       <c r="D4484" t="s">
-        <v>4181</v>
+        <v>4418</v>
       </c>
     </row>
     <row r="4485" spans="3:5">
       <c r="D4485" t="s">
-        <v>4023</v>
+        <v>4186</v>
       </c>
     </row>
     <row r="4486" spans="3:5">
-      <c r="E4486" t="s">
-        <v>4182</v>
+      <c r="D4486" t="s">
+        <v>4187</v>
       </c>
     </row>
     <row r="4487" spans="3:5">
       <c r="D4487" t="s">
-        <v>4183</v>
+        <v>4188</v>
       </c>
     </row>
     <row r="4488" spans="3:5">
       <c r="D4488" t="s">
-        <v>4184</v>
+        <v>4189</v>
       </c>
     </row>
     <row r="4489" spans="3:5">
-      <c r="D4489" t="s">
-        <v>4185</v>
+      <c r="C4489" t="s">
+        <v>2930</v>
       </c>
     </row>
     <row r="4490" spans="3:5">
-      <c r="C4490" t="s">
-        <v>2893</v>
+      <c r="D4490" t="s">
+        <v>4419</v>
       </c>
     </row>
     <row r="4491" spans="3:5">
       <c r="D4491" t="s">
-        <v>4418</v>
+        <v>4190</v>
       </c>
     </row>
     <row r="4492" spans="3:5">
       <c r="D4492" t="s">
-        <v>4186</v>
+        <v>4191</v>
       </c>
     </row>
     <row r="4493" spans="3:5">
       <c r="D4493" t="s">
-        <v>4187</v>
+        <v>4192</v>
       </c>
     </row>
     <row r="4494" spans="3:5">
       <c r="D4494" t="s">
-        <v>4188</v>
+        <v>4193</v>
       </c>
     </row>
     <row r="4495" spans="3:5">
       <c r="D4495" t="s">
-        <v>4189</v>
+        <v>4024</v>
       </c>
     </row>
     <row r="4496" spans="3:5">
-      <c r="C4496" t="s">
-        <v>2930</v>
+      <c r="E4496" t="s">
+        <v>2776</v>
       </c>
     </row>
     <row r="4497" spans="3:5">
-      <c r="D4497" t="s">
-        <v>4419</v>
+      <c r="E4497" t="s">
+        <v>4025</v>
       </c>
     </row>
     <row r="4498" spans="3:5">
-      <c r="D4498" t="s">
-        <v>4190</v>
+      <c r="C4498" t="s">
+        <v>2944</v>
       </c>
     </row>
     <row r="4499" spans="3:5">
       <c r="D4499" t="s">
-        <v>4191</v>
+        <v>4420</v>
       </c>
     </row>
     <row r="4500" spans="3:5">
       <c r="D4500" t="s">
-        <v>4192</v>
+        <v>4194</v>
       </c>
     </row>
     <row r="4501" spans="3:5">
       <c r="D4501" t="s">
-        <v>4193</v>
+        <v>4195</v>
       </c>
     </row>
     <row r="4502" spans="3:5">
       <c r="D4502" t="s">
-        <v>4024</v>
+        <v>4196</v>
       </c>
     </row>
     <row r="4503" spans="3:5">
-      <c r="E4503" t="s">
-        <v>2776</v>
+      <c r="C4503" t="s">
+        <v>2960</v>
       </c>
     </row>
     <row r="4504" spans="3:5">
-      <c r="E4504" t="s">
-        <v>4025</v>
+      <c r="D4504" t="s">
+        <v>4421</v>
       </c>
     </row>
     <row r="4505" spans="3:5">
-      <c r="C4505" t="s">
-        <v>2944</v>
+      <c r="D4505" t="s">
+        <v>4026</v>
       </c>
     </row>
     <row r="4506" spans="3:5">
-      <c r="D4506" t="s">
-        <v>4420</v>
+      <c r="E4506" t="s">
+        <v>2809</v>
       </c>
     </row>
     <row r="4507" spans="3:5">
       <c r="D4507" t="s">
-        <v>4194</v>
+        <v>4197</v>
       </c>
     </row>
     <row r="4508" spans="3:5">
       <c r="D4508" t="s">
-        <v>4195</v>
+        <v>4198</v>
       </c>
     </row>
     <row r="4509" spans="3:5">
       <c r="D4509" t="s">
-        <v>4196</v>
+        <v>4437</v>
       </c>
     </row>
     <row r="4510" spans="3:5">
-      <c r="C4510" t="s">
-        <v>2960</v>
+      <c r="D4510" t="s">
+        <v>4199</v>
       </c>
     </row>
     <row r="4511" spans="3:5">
       <c r="D4511" t="s">
-        <v>4421</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="4512" spans="3:5">
-      <c r="D4512" t="s">
-        <v>4026</v>
+      <c r="C4512" t="s">
+        <v>2991</v>
       </c>
     </row>
     <row r="4513" spans="3:5">
-      <c r="E4513" t="s">
-        <v>2809</v>
+      <c r="D4513" t="s">
+        <v>4422</v>
       </c>
     </row>
     <row r="4514" spans="3:5">
       <c r="D4514" t="s">
-        <v>4197</v>
+        <v>4201</v>
       </c>
     </row>
     <row r="4515" spans="3:5">
       <c r="D4515" t="s">
-        <v>4198</v>
+        <v>4202</v>
       </c>
     </row>
     <row r="4516" spans="3:5">
       <c r="D4516" t="s">
-        <v>4437</v>
+        <v>4027</v>
       </c>
     </row>
     <row r="4517" spans="3:5">
-      <c r="D4517" t="s">
-        <v>4199</v>
+      <c r="E4517" t="s">
+        <v>4028</v>
       </c>
     </row>
     <row r="4518" spans="3:5">
-      <c r="D4518" t="s">
-        <v>4200</v>
+      <c r="C4518" t="s">
+        <v>3023</v>
       </c>
     </row>
     <row r="4519" spans="3:5">
-      <c r="C4519" t="s">
-        <v>2991</v>
+      <c r="D4519" t="s">
+        <v>4423</v>
       </c>
     </row>
     <row r="4520" spans="3:5">
       <c r="D4520" t="s">
-        <v>4422</v>
+        <v>4203</v>
       </c>
     </row>
     <row r="4521" spans="3:5">
       <c r="D4521" t="s">
-        <v>4201</v>
+        <v>4029</v>
       </c>
     </row>
     <row r="4522" spans="3:5">
-      <c r="D4522" t="s">
-        <v>4202</v>
+      <c r="E4522" t="s">
+        <v>4030</v>
       </c>
     </row>
     <row r="4523" spans="3:5">
       <c r="D4523" t="s">
-        <v>4027</v>
+        <v>4031</v>
       </c>
     </row>
     <row r="4524" spans="3:5">
       <c r="E4524" t="s">
-        <v>4028</v>
+        <v>4032</v>
       </c>
     </row>
     <row r="4525" spans="3:5">
-      <c r="C4525" t="s">
-        <v>3023</v>
+      <c r="D4525" t="s">
+        <v>4033</v>
       </c>
     </row>
     <row r="4526" spans="3:5">
-      <c r="D4526" t="s">
-        <v>4423</v>
+      <c r="E4526" t="s">
+        <v>4034</v>
       </c>
     </row>
     <row r="4527" spans="3:5">
       <c r="D4527" t="s">
-        <v>4203</v>
+        <v>4035</v>
       </c>
     </row>
     <row r="4528" spans="3:5">
-      <c r="D4528" t="s">
-        <v>4029</v>
+      <c r="E4528" t="s">
+        <v>4036</v>
       </c>
     </row>
     <row r="4529" spans="3:5">
-      <c r="E4529" t="s">
-        <v>4030</v>
+      <c r="D4529" t="s">
+        <v>4037</v>
       </c>
     </row>
     <row r="4530" spans="3:5">
-      <c r="D4530" t="s">
-        <v>4031</v>
+      <c r="E4530" t="s">
+        <v>4038</v>
       </c>
     </row>
     <row r="4531" spans="3:5">
-      <c r="E4531" t="s">
-        <v>4032</v>
+      <c r="C4531" t="s">
+        <v>3044</v>
       </c>
     </row>
     <row r="4532" spans="3:5">
       <c r="D4532" t="s">
-        <v>4033</v>
+        <v>4424</v>
       </c>
     </row>
     <row r="4533" spans="3:5">
-      <c r="E4533" t="s">
-        <v>4034</v>
+      <c r="D4533" t="s">
+        <v>4204</v>
       </c>
     </row>
     <row r="4534" spans="3:5">
       <c r="D4534" t="s">
-        <v>4035</v>
+        <v>4205</v>
       </c>
     </row>
     <row r="4535" spans="3:5">
-      <c r="E4535" t="s">
-        <v>4036</v>
+      <c r="C4535" t="s">
+        <v>3060</v>
       </c>
     </row>
     <row r="4536" spans="3:5">
       <c r="D4536" t="s">
-        <v>4037</v>
+        <v>4425</v>
       </c>
     </row>
     <row r="4537" spans="3:5">
-      <c r="E4537" t="s">
-        <v>4038</v>
+      <c r="D4537" t="s">
+        <v>4206</v>
       </c>
     </row>
     <row r="4538" spans="3:5">
-      <c r="C4538" t="s">
-        <v>3044</v>
+      <c r="D4538" t="s">
+        <v>4207</v>
       </c>
     </row>
     <row r="4539" spans="3:5">
       <c r="D4539" t="s">
-        <v>4424</v>
+        <v>4208</v>
       </c>
     </row>
     <row r="4540" spans="3:5">
       <c r="D4540" t="s">
-        <v>4204</v>
+        <v>4209</v>
       </c>
     </row>
     <row r="4541" spans="3:5">
       <c r="D4541" t="s">
-        <v>4205</v>
+        <v>4210</v>
       </c>
     </row>
     <row r="4542" spans="3:5">
-      <c r="C4542" t="s">
-        <v>3060</v>
+      <c r="D4542" t="s">
+        <v>4211</v>
       </c>
     </row>
     <row r="4543" spans="3:5">
       <c r="D4543" t="s">
-        <v>4425</v>
+        <v>4212</v>
       </c>
     </row>
     <row r="4544" spans="3:5">
       <c r="D4544" t="s">
-        <v>4206</v>
-      </c>
-    </row>
-    <row r="4545" spans="4:4">
+        <v>4213</v>
+      </c>
+    </row>
+    <row r="4545" spans="3:5">
       <c r="D4545" t="s">
-        <v>4207</v>
-      </c>
-    </row>
-    <row r="4546" spans="4:4">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="4546" spans="3:5">
       <c r="D4546" t="s">
-        <v>4208</v>
-      </c>
-    </row>
-    <row r="4547" spans="4:4">
+        <v>4215</v>
+      </c>
+    </row>
+    <row r="4547" spans="3:5">
       <c r="D4547" t="s">
-        <v>4209</v>
-      </c>
-    </row>
-    <row r="4548" spans="4:4">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="4548" spans="3:5">
       <c r="D4548" t="s">
-        <v>4210</v>
-      </c>
-    </row>
-    <row r="4549" spans="4:4">
+        <v>4217</v>
+      </c>
+    </row>
+    <row r="4549" spans="3:5">
       <c r="D4549" t="s">
-        <v>4211</v>
-      </c>
-    </row>
-    <row r="4550" spans="4:4">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="4550" spans="3:5">
       <c r="D4550" t="s">
-        <v>4212</v>
-      </c>
-    </row>
-    <row r="4551" spans="4:4">
+        <v>4219</v>
+      </c>
+    </row>
+    <row r="4551" spans="3:5">
       <c r="D4551" t="s">
-        <v>4213</v>
-      </c>
-    </row>
-    <row r="4552" spans="4:4">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="4552" spans="3:5">
       <c r="D4552" t="s">
-        <v>4214</v>
-      </c>
-    </row>
-    <row r="4553" spans="4:4">
+        <v>4221</v>
+      </c>
+    </row>
+    <row r="4553" spans="3:5">
       <c r="D4553" t="s">
-        <v>4215</v>
-      </c>
-    </row>
-    <row r="4554" spans="4:4">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="4554" spans="3:5">
       <c r="D4554" t="s">
-        <v>4216</v>
-      </c>
-    </row>
-    <row r="4555" spans="4:4">
-      <c r="D4555" t="s">
-        <v>4217</v>
-      </c>
-    </row>
-    <row r="4556" spans="4:4">
+        <v>4039</v>
+      </c>
+    </row>
+    <row r="4555" spans="3:5">
+      <c r="E4555" t="s">
+        <v>4040</v>
+      </c>
+    </row>
+    <row r="4556" spans="3:5">
       <c r="D4556" t="s">
-        <v>4218</v>
-      </c>
-    </row>
-    <row r="4557" spans="4:4">
+        <v>4223</v>
+      </c>
+    </row>
+    <row r="4557" spans="3:5">
       <c r="D4557" t="s">
-        <v>4219</v>
-      </c>
-    </row>
-    <row r="4558" spans="4:4">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="4558" spans="3:5">
       <c r="D4558" t="s">
-        <v>4220</v>
-      </c>
-    </row>
-    <row r="4559" spans="4:4">
-      <c r="D4559" t="s">
-        <v>4221</v>
-      </c>
-    </row>
-    <row r="4560" spans="4:4">
+        <v>4225</v>
+      </c>
+    </row>
+    <row r="4559" spans="3:5">
+      <c r="C4559" t="s">
+        <v>3068</v>
+      </c>
+    </row>
+    <row r="4560" spans="3:5">
       <c r="D4560" t="s">
-        <v>4222</v>
-      </c>
-    </row>
-    <row r="4561" spans="3:5">
+        <v>4426</v>
+      </c>
+    </row>
+    <row r="4561" spans="2:4">
       <c r="D4561" t="s">
-        <v>4039</v>
-      </c>
-    </row>
-    <row r="4562" spans="3:5">
-      <c r="E4562" t="s">
-        <v>4040</v>
-      </c>
-    </row>
-    <row r="4563" spans="3:5">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="4562" spans="2:4">
+      <c r="C4562" t="s">
+        <v>3109</v>
+      </c>
+    </row>
+    <row r="4563" spans="2:4">
       <c r="D4563" t="s">
-        <v>4223</v>
-      </c>
-    </row>
-    <row r="4564" spans="3:5">
+        <v>4427</v>
+      </c>
+    </row>
+    <row r="4564" spans="2:4">
       <c r="D4564" t="s">
-        <v>4224</v>
-      </c>
-    </row>
-    <row r="4565" spans="3:5">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="4565" spans="2:4">
       <c r="D4565" t="s">
-        <v>4225</v>
-      </c>
-    </row>
-    <row r="4566" spans="3:5">
+        <v>4227</v>
+      </c>
+    </row>
+    <row r="4566" spans="2:4">
       <c r="C4566" t="s">
-        <v>3068</v>
-      </c>
-    </row>
-    <row r="4567" spans="3:5">
+        <v>3132</v>
+      </c>
+    </row>
+    <row r="4567" spans="2:4">
       <c r="D4567" t="s">
-        <v>4426</v>
-      </c>
-    </row>
-    <row r="4568" spans="3:5">
+        <v>4443</v>
+      </c>
+    </row>
+    <row r="4568" spans="2:4">
       <c r="D4568" t="s">
-        <v>4226</v>
-      </c>
-    </row>
-    <row r="4569" spans="3:5">
-      <c r="C4569" t="s">
-        <v>3109</v>
-      </c>
-    </row>
-    <row r="4570" spans="3:5">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="4569" spans="2:4">
+      <c r="D4569" t="s">
+        <v>4229</v>
+      </c>
+    </row>
+    <row r="4570" spans="2:4">
       <c r="D4570" t="s">
-        <v>4427</v>
-      </c>
-    </row>
-    <row r="4571" spans="3:5">
-      <c r="D4571" t="s">
-        <v>4442</v>
-      </c>
-    </row>
-    <row r="4572" spans="3:5">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="4571" spans="2:4">
+      <c r="C4571" t="s">
+        <v>3183</v>
+      </c>
+    </row>
+    <row r="4572" spans="2:4">
       <c r="D4572" t="s">
-        <v>4227</v>
-      </c>
-    </row>
-    <row r="4573" spans="3:5">
-      <c r="C4573" t="s">
-        <v>3132</v>
-      </c>
-    </row>
-    <row r="4574" spans="3:5">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="4573" spans="2:4">
+      <c r="D4573" t="s">
+        <v>4231</v>
+      </c>
+    </row>
+    <row r="4574" spans="2:4">
       <c r="D4574" t="s">
-        <v>4443</v>
-      </c>
-    </row>
-    <row r="4575" spans="3:5">
-      <c r="D4575" t="s">
-        <v>4228</v>
-      </c>
-    </row>
-    <row r="4576" spans="3:5">
-      <c r="D4576" t="s">
-        <v>4229</v>
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="4575" spans="2:4">
+      <c r="B4575" t="s">
+        <v>4041</v>
+      </c>
+    </row>
+    <row r="4576" spans="2:4">
+      <c r="C4576" t="s">
+        <v>4042</v>
       </c>
     </row>
     <row r="4577" spans="2:5">
       <c r="D4577" t="s">
-        <v>4230</v>
+        <v>4447</v>
       </c>
     </row>
     <row r="4578" spans="2:5">
       <c r="C4578" t="s">
-        <v>3183</v>
+        <v>4043</v>
       </c>
     </row>
     <row r="4579" spans="2:5">
       <c r="D4579" t="s">
-        <v>4428</v>
+        <v>4429</v>
       </c>
     </row>
     <row r="4580" spans="2:5">
       <c r="D4580" t="s">
-        <v>4231</v>
+        <v>4279</v>
       </c>
     </row>
     <row r="4581" spans="2:5">
-      <c r="D4581" t="s">
-        <v>4232</v>
+      <c r="B4581" t="s">
+        <v>4280</v>
       </c>
     </row>
     <row r="4582" spans="2:5">
-      <c r="B4582" t="s">
-        <v>4041</v>
+      <c r="C4582" t="s">
+        <v>4044</v>
       </c>
     </row>
     <row r="4583" spans="2:5">
-      <c r="C4583" t="s">
-        <v>4042</v>
+      <c r="D4583" t="s">
+        <v>4276</v>
       </c>
     </row>
     <row r="4584" spans="2:5">
-      <c r="D4584" t="s">
-        <v>4447</v>
+      <c r="E4584" t="s">
+        <v>4233</v>
       </c>
     </row>
     <row r="4585" spans="2:5">
-      <c r="C4585" t="s">
-        <v>4043</v>
+      <c r="E4585" t="s">
+        <v>4234</v>
       </c>
     </row>
     <row r="4586" spans="2:5">
-      <c r="D4586" t="s">
-        <v>4429</v>
+      <c r="E4586" t="s">
+        <v>4235</v>
       </c>
     </row>
     <row r="4587" spans="2:5">
-      <c r="D4587" t="s">
-        <v>4279</v>
+      <c r="E4587" t="s">
+        <v>4236</v>
       </c>
     </row>
     <row r="4588" spans="2:5">
-      <c r="B4588" t="s">
-        <v>4280</v>
+      <c r="E4588" t="s">
+        <v>4237</v>
       </c>
     </row>
     <row r="4589" spans="2:5">
-      <c r="C4589" t="s">
-        <v>4044</v>
+      <c r="E4589" t="s">
+        <v>4238</v>
       </c>
     </row>
     <row r="4590" spans="2:5">
-      <c r="D4590" t="s">
-        <v>4276</v>
+      <c r="E4590" t="s">
+        <v>4239</v>
       </c>
     </row>
     <row r="4591" spans="2:5">
-      <c r="E4591" t="s">
-        <v>4233</v>
+      <c r="D4591" t="s">
+        <v>4277</v>
       </c>
     </row>
     <row r="4592" spans="2:5">
       <c r="E4592" t="s">
-        <v>4234</v>
+        <v>4240</v>
       </c>
     </row>
     <row r="4593" spans="4:5">
       <c r="E4593" t="s">
-        <v>4235</v>
+        <v>4241</v>
       </c>
     </row>
     <row r="4594" spans="4:5">
       <c r="E4594" t="s">
-        <v>4236</v>
+        <v>4242</v>
       </c>
     </row>
     <row r="4595" spans="4:5">
       <c r="E4595" t="s">
-        <v>4237</v>
+        <v>4243</v>
       </c>
     </row>
     <row r="4596" spans="4:5">
       <c r="E4596" t="s">
-        <v>4238</v>
+        <v>4244</v>
       </c>
     </row>
     <row r="4597" spans="4:5">
       <c r="E4597" t="s">
-        <v>4239</v>
+        <v>4245</v>
       </c>
     </row>
     <row r="4598" spans="4:5">
-      <c r="D4598" t="s">
-        <v>4277</v>
+      <c r="E4598" t="s">
+        <v>4246</v>
       </c>
     </row>
     <row r="4599" spans="4:5">
-      <c r="E4599" t="s">
-        <v>4240</v>
+      <c r="D4599" t="s">
+        <v>4278</v>
       </c>
     </row>
     <row r="4600" spans="4:5">
       <c r="E4600" t="s">
-        <v>4241</v>
+        <v>4247</v>
       </c>
     </row>
     <row r="4601" spans="4:5">
       <c r="E4601" t="s">
-        <v>4242</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="4602" spans="4:5">
       <c r="E4602" t="s">
-        <v>4243</v>
+        <v>4249</v>
       </c>
     </row>
     <row r="4603" spans="4:5">
       <c r="E4603" t="s">
-        <v>4244</v>
+        <v>4250</v>
       </c>
     </row>
     <row r="4604" spans="4:5">
       <c r="E4604" t="s">
-        <v>4245</v>
+        <v>4251</v>
       </c>
     </row>
     <row r="4605" spans="4:5">
       <c r="E4605" t="s">
-        <v>4246</v>
+        <v>4252</v>
       </c>
     </row>
     <row r="4606" spans="4:5">
-      <c r="D4606" t="s">
-        <v>4278</v>
+      <c r="E4606" t="s">
+        <v>4253</v>
       </c>
     </row>
     <row r="4607" spans="4:5">
       <c r="E4607" t="s">
-        <v>4247</v>
+        <v>4254</v>
       </c>
     </row>
     <row r="4608" spans="4:5">
       <c r="E4608" t="s">
-        <v>4248</v>
+        <v>4255</v>
       </c>
     </row>
     <row r="4609" spans="3:5">
       <c r="E4609" t="s">
-        <v>4249</v>
+        <v>4256</v>
       </c>
     </row>
     <row r="4610" spans="3:5">
       <c r="E4610" t="s">
-        <v>4250</v>
+        <v>4257</v>
       </c>
     </row>
     <row r="4611" spans="3:5">
       <c r="E4611" t="s">
-        <v>4251</v>
+        <v>4258</v>
       </c>
     </row>
     <row r="4612" spans="3:5">
-      <c r="E4612" t="s">
-        <v>4252</v>
+      <c r="C4612" t="s">
+        <v>4045</v>
       </c>
     </row>
     <row r="4613" spans="3:5">
-      <c r="E4613" t="s">
-        <v>4253</v>
+      <c r="D4613" t="s">
+        <v>4259</v>
       </c>
     </row>
     <row r="4614" spans="3:5">
-      <c r="E4614" t="s">
-        <v>4254</v>
+      <c r="D4614" t="s">
+        <v>4260</v>
       </c>
     </row>
     <row r="4615" spans="3:5">
-      <c r="E4615" t="s">
-        <v>4255</v>
+      <c r="D4615" t="s">
+        <v>4261</v>
       </c>
     </row>
     <row r="4616" spans="3:5">
-      <c r="E4616" t="s">
-        <v>4256</v>
+      <c r="D4616" t="s">
+        <v>4262</v>
       </c>
     </row>
     <row r="4617" spans="3:5">
-      <c r="E4617" t="s">
-        <v>4257</v>
+      <c r="D4617" t="s">
+        <v>4263</v>
       </c>
     </row>
     <row r="4618" spans="3:5">
-      <c r="E4618" t="s">
-        <v>4258</v>
+      <c r="C4618" t="s">
+        <v>4046</v>
       </c>
     </row>
     <row r="4619" spans="3:5">
-      <c r="C4619" t="s">
-        <v>4045</v>
+      <c r="D4619" t="s">
+        <v>4264</v>
       </c>
     </row>
     <row r="4620" spans="3:5">
       <c r="D4620" t="s">
-        <v>4259</v>
+        <v>4265</v>
       </c>
     </row>
     <row r="4621" spans="3:5">
       <c r="D4621" t="s">
-        <v>4260</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="4622" spans="3:5">
       <c r="D4622" t="s">
-        <v>4261</v>
+        <v>4267</v>
       </c>
     </row>
     <row r="4623" spans="3:5">
       <c r="D4623" t="s">
-        <v>4262</v>
+        <v>4268</v>
       </c>
     </row>
     <row r="4624" spans="3:5">
       <c r="D4624" t="s">
-        <v>4263</v>
+        <v>4269</v>
       </c>
     </row>
     <row r="4625" spans="2:4">
-      <c r="C4625" t="s">
-        <v>4046</v>
+      <c r="D4625" t="s">
+        <v>4270</v>
       </c>
     </row>
     <row r="4626" spans="2:4">
       <c r="D4626" t="s">
-        <v>4264</v>
+        <v>4271</v>
       </c>
     </row>
     <row r="4627" spans="2:4">
       <c r="D4627" t="s">
-        <v>4265</v>
+        <v>4272</v>
       </c>
     </row>
     <row r="4628" spans="2:4">
       <c r="D4628" t="s">
-        <v>4266</v>
+        <v>4273</v>
       </c>
     </row>
     <row r="4629" spans="2:4">
       <c r="D4629" t="s">
-        <v>4267</v>
+        <v>4274</v>
       </c>
     </row>
     <row r="4630" spans="2:4">
-      <c r="D4630" t="s">
-        <v>4268</v>
+      <c r="B4630" t="s">
+        <v>4281</v>
       </c>
     </row>
     <row r="4631" spans="2:4">
-      <c r="D4631" t="s">
-        <v>4269</v>
+      <c r="C4631" t="s">
+        <v>4282</v>
       </c>
     </row>
     <row r="4632" spans="2:4">
-      <c r="D4632" t="s">
-        <v>4270</v>
+      <c r="B4632" t="s">
+        <v>4434</v>
       </c>
     </row>
     <row r="4633" spans="2:4">
-      <c r="D4633" t="s">
-        <v>4271</v>
-      </c>
+      <c r="C4633" s="1" t="s">
+        <v>4430</v>
+      </c>
+      <c r="D4633" s="1"/>
     </row>
     <row r="4634" spans="2:4">
-      <c r="D4634" t="s">
-        <v>4272</v>
-      </c>
+      <c r="C4634" t="s">
+        <v>4431</v>
+      </c>
+      <c r="D4634" s="1"/>
     </row>
     <row r="4635" spans="2:4">
-      <c r="D4635" t="s">
-        <v>4273</v>
+      <c r="C4635" s="1"/>
+      <c r="D4635" s="2" t="s">
+        <v>4449</v>
       </c>
     </row>
     <row r="4636" spans="2:4">
-      <c r="D4636" t="s">
-        <v>4274</v>
+      <c r="C4636" s="1"/>
+      <c r="D4636" s="2" t="s">
+        <v>4450</v>
       </c>
     </row>
     <row r="4637" spans="2:4">
-      <c r="B4637" t="s">
-        <v>4281</v>
+      <c r="C4637" s="1"/>
+      <c r="D4637" s="2" t="s">
+        <v>4451</v>
       </c>
     </row>
     <row r="4638" spans="2:4">
-      <c r="C4638" t="s">
-        <v>4282</v>
+      <c r="C4638" s="1"/>
+      <c r="D4638" s="2" t="s">
+        <v>4452</v>
       </c>
     </row>
     <row r="4639" spans="2:4">
-      <c r="B4639" t="s">
-        <v>4434</v>
+      <c r="C4639" s="1"/>
+      <c r="D4639" s="2" t="s">
+        <v>4453</v>
       </c>
     </row>
     <row r="4640" spans="2:4">
-      <c r="C4640" s="1" t="s">
-        <v>4430</v>
-      </c>
-      <c r="D4640" s="1"/>
+      <c r="C4640" s="1"/>
+      <c r="D4640" s="2" t="s">
+        <v>4454</v>
+      </c>
     </row>
     <row r="4641" spans="3:4">
-      <c r="C4641" t="s">
-        <v>4431</v>
-      </c>
-      <c r="D4641" s="1"/>
+      <c r="C4641" s="1"/>
+      <c r="D4641" s="2" t="s">
+        <v>4455</v>
+      </c>
     </row>
     <row r="4642" spans="3:4">
-      <c r="C4642" s="1"/>
-      <c r="D4642" s="2" t="s">
-        <v>4449</v>
-      </c>
+      <c r="C4642" t="s">
+        <v>4432</v>
+      </c>
+      <c r="D4642" s="1"/>
     </row>
     <row r="4643" spans="3:4">
       <c r="C4643" s="1"/>
-      <c r="D4643" s="2" t="s">
-        <v>4450</v>
+      <c r="D4643" t="s">
+        <v>4456</v>
       </c>
     </row>
     <row r="4644" spans="3:4">
       <c r="C4644" s="1"/>
-      <c r="D4644" s="2" t="s">
-        <v>4451</v>
+      <c r="D4644" t="s">
+        <v>4457</v>
       </c>
     </row>
     <row r="4645" spans="3:4">
       <c r="C4645" s="1"/>
-      <c r="D4645" s="2" t="s">
-        <v>4452</v>
+      <c r="D4645" t="s">
+        <v>4458</v>
       </c>
     </row>
     <row r="4646" spans="3:4">
-      <c r="C4646" s="1"/>
-      <c r="D4646" s="2" t="s">
-        <v>4453</v>
-      </c>
+      <c r="C4646" t="s">
+        <v>3492</v>
+      </c>
+      <c r="D4646" s="1"/>
     </row>
     <row r="4647" spans="3:4">
       <c r="C4647" s="1"/>
-      <c r="D4647" s="2" t="s">
-        <v>4454</v>
+      <c r="D4647" t="s">
+        <v>4459</v>
       </c>
     </row>
     <row r="4648" spans="3:4">
       <c r="C4648" s="1"/>
-      <c r="D4648" s="2" t="s">
-        <v>4455</v>
+      <c r="D4648" t="s">
+        <v>4460</v>
       </c>
     </row>
     <row r="4649" spans="3:4">
-      <c r="C4649" t="s">
-        <v>4432</v>
-      </c>
-      <c r="D4649" s="1"/>
+      <c r="C4649" s="1"/>
+      <c r="D4649" t="s">
+        <v>4461</v>
+      </c>
     </row>
     <row r="4650" spans="3:4">
       <c r="C4650" s="1"/>
       <c r="D4650" t="s">
-        <v>4456</v>
+        <v>4462</v>
       </c>
     </row>
     <row r="4651" spans="3:4">
-      <c r="C4651" s="1"/>
-      <c r="D4651" t="s">
-        <v>4457</v>
-      </c>
+      <c r="C4651" t="s">
+        <v>4433</v>
+      </c>
+      <c r="D4651" s="1"/>
     </row>
     <row r="4652" spans="3:4">
       <c r="C4652" s="1"/>
       <c r="D4652" t="s">
-        <v>4458</v>
+        <v>4463</v>
       </c>
     </row>
     <row r="4653" spans="3:4">
-      <c r="C4653" t="s">
-        <v>3492</v>
-      </c>
-      <c r="D4653" s="1"/>
+      <c r="D4653" t="s">
+        <v>4464</v>
+      </c>
     </row>
     <row r="4654" spans="3:4">
-      <c r="C4654" s="1"/>
       <c r="D4654" t="s">
-        <v>4459</v>
+        <v>4465</v>
       </c>
     </row>
     <row r="4655" spans="3:4">
-      <c r="C4655" s="1"/>
       <c r="D4655" t="s">
-        <v>4460</v>
+        <v>4466</v>
       </c>
     </row>
     <row r="4656" spans="3:4">
-      <c r="C4656" s="1"/>
       <c r="D4656" t="s">
-        <v>4461</v>
+        <v>4467</v>
       </c>
     </row>
     <row r="4657" spans="2:4">
-      <c r="C4657" s="1"/>
       <c r="D4657" t="s">
-        <v>4462</v>
+        <v>4468</v>
       </c>
     </row>
     <row r="4658" spans="2:4">
-      <c r="C4658" t="s">
-        <v>4433</v>
-      </c>
-      <c r="D4658" s="1"/>
-    </row>
-    <row r="4659" spans="2:4">
-      <c r="C4659" s="1"/>
-      <c r="D4659" t="s">
-        <v>4463</v>
-      </c>
+      <c r="B4658" t="s">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="4659" spans="2:4" ht="19.8">
+      <c r="C4659" t="s">
+        <v>4471</v>
+      </c>
+      <c r="D4659" s="1"/>
     </row>
     <row r="4660" spans="2:4">
-      <c r="D4660" t="s">
-        <v>4464</v>
-      </c>
+      <c r="C4660" s="1" t="s">
+        <v>4472</v>
+      </c>
+      <c r="D4660" s="1"/>
     </row>
     <row r="4661" spans="2:4">
-      <c r="D4661" t="s">
-        <v>4465</v>
-      </c>
+      <c r="C4661" s="1" t="s">
+        <v>4473</v>
+      </c>
+      <c r="D4661" s="1"/>
     </row>
     <row r="4662" spans="2:4">
-      <c r="D4662" t="s">
-        <v>4466</v>
-      </c>
-    </row>
-    <row r="4663" spans="2:4">
-      <c r="D4663" t="s">
-        <v>4467</v>
-      </c>
-    </row>
-    <row r="4664" spans="2:4">
-      <c r="D4664" t="s">
-        <v>4468</v>
-      </c>
-    </row>
-    <row r="4665" spans="2:4">
-      <c r="B4665" t="s">
-        <v>4470</v>
-      </c>
-    </row>
-    <row r="4666" spans="2:4" ht="19.8">
-      <c r="C4666" t="s">
-        <v>4471</v>
-      </c>
-      <c r="D4666" s="1"/>
+      <c r="C4662" s="1" t="s">
+        <v>4474</v>
+      </c>
+      <c r="D4662" s="1"/>
+    </row>
+    <row r="4663" spans="2:4" s="1" customFormat="1">
+      <c r="D4663" s="1" t="s">
+        <v>4475</v>
+      </c>
+    </row>
+    <row r="4664" spans="2:4" s="1" customFormat="1">
+      <c r="D4664" s="1" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="4665" spans="2:4" s="1" customFormat="1">
+      <c r="D4665" s="1" t="s">
+        <v>4477</v>
+      </c>
+    </row>
+    <row r="4666" spans="2:4">
+      <c r="C4666" s="1"/>
+      <c r="D4666" s="1" t="s">
+        <v>4478</v>
+      </c>
     </row>
     <row r="4667" spans="2:4">
-      <c r="C4667" s="1" t="s">
-        <v>4472</v>
-      </c>
-      <c r="D4667" s="1"/>
+      <c r="C4667" s="1"/>
+      <c r="D4667" s="1" t="s">
+        <v>4479</v>
+      </c>
     </row>
     <row r="4668" spans="2:4">
-      <c r="C4668" s="1" t="s">
-        <v>4473</v>
-      </c>
-      <c r="D4668" s="1"/>
+      <c r="C4668" s="1"/>
+      <c r="D4668" s="1" t="s">
+        <v>4480</v>
+      </c>
     </row>
     <row r="4669" spans="2:4">
-      <c r="C4669" s="1" t="s">
-        <v>4474</v>
-      </c>
-      <c r="D4669" s="1"/>
-    </row>
-    <row r="4670" spans="2:4" s="1" customFormat="1">
+      <c r="C4669" s="1"/>
+      <c r="D4669" s="1" t="s">
+        <v>4481</v>
+      </c>
+    </row>
+    <row r="4670" spans="2:4">
+      <c r="C4670" s="1"/>
       <c r="D4670" s="1" t="s">
-        <v>4475</v>
-      </c>
-    </row>
-    <row r="4671" spans="2:4" s="1" customFormat="1">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="4671" spans="2:4">
+      <c r="C4671" s="1"/>
       <c r="D4671" s="1" t="s">
-        <v>4476</v>
-      </c>
-    </row>
-    <row r="4672" spans="2:4" s="1" customFormat="1">
+        <v>4483</v>
+      </c>
+    </row>
+    <row r="4672" spans="2:4">
+      <c r="C4672" s="1"/>
       <c r="D4672" s="1" t="s">
-        <v>4477</v>
+        <v>4484</v>
       </c>
     </row>
     <row r="4673" spans="3:4">
       <c r="C4673" s="1"/>
       <c r="D4673" s="1" t="s">
-        <v>4478</v>
+        <v>4485</v>
       </c>
     </row>
     <row r="4674" spans="3:4">
       <c r="C4674" s="1"/>
       <c r="D4674" s="1" t="s">
-        <v>4479</v>
+        <v>4486</v>
       </c>
     </row>
     <row r="4675" spans="3:4">
       <c r="C4675" s="1"/>
       <c r="D4675" s="1" t="s">
-        <v>4480</v>
+        <v>4488</v>
       </c>
     </row>
     <row r="4676" spans="3:4">
       <c r="C4676" s="1"/>
-      <c r="D4676" s="1" t="s">
-        <v>4481</v>
+      <c r="D4676" s="3" t="s">
+        <v>4487</v>
       </c>
     </row>
     <row r="4677" spans="3:4">
       <c r="C4677" s="1"/>
-      <c r="D4677" s="1" t="s">
-        <v>4482</v>
+      <c r="D4677" s="3" t="s">
+        <v>4489</v>
       </c>
     </row>
     <row r="4678" spans="3:4">
       <c r="C4678" s="1"/>
-      <c r="D4678" s="1" t="s">
-        <v>4483</v>
+      <c r="D4678" s="3" t="s">
+        <v>4490</v>
       </c>
     </row>
     <row r="4679" spans="3:4">
       <c r="C4679" s="1"/>
-      <c r="D4679" s="1" t="s">
-        <v>4484</v>
+      <c r="D4679" t="s">
+        <v>4491</v>
       </c>
     </row>
     <row r="4680" spans="3:4">
-      <c r="C4680" s="1"/>
-      <c r="D4680" s="1" t="s">
-        <v>4485</v>
+      <c r="C4680" s="1" t="s">
+        <v>4493</v>
       </c>
     </row>
     <row r="4681" spans="3:4">
       <c r="C4681" s="1"/>
-      <c r="D4681" s="1" t="s">
-        <v>4486</v>
+      <c r="D4681" t="s">
+        <v>4492</v>
       </c>
     </row>
     <row r="4682" spans="3:4">
       <c r="C4682" s="1"/>
-      <c r="D4682" s="1" t="s">
-        <v>4488</v>
+      <c r="D4682" t="s">
+        <v>4494</v>
       </c>
     </row>
     <row r="4683" spans="3:4">
       <c r="C4683" s="1"/>
-      <c r="D4683" s="3" t="s">
-        <v>4487</v>
+      <c r="D4683" t="s">
+        <v>4495</v>
       </c>
     </row>
     <row r="4684" spans="3:4">
-      <c r="C4684" s="1"/>
-      <c r="D4684" s="3" t="s">
-        <v>4489</v>
-      </c>
-    </row>
-    <row r="4685" spans="3:4">
-      <c r="C4685" s="1"/>
-      <c r="D4685" s="3" t="s">
-        <v>4490</v>
-      </c>
-    </row>
-    <row r="4686" spans="3:4">
-      <c r="C4686" s="1"/>
-      <c r="D4686" t="s">
-        <v>4491</v>
-      </c>
-    </row>
-    <row r="4687" spans="3:4">
-      <c r="C4687" s="1" t="s">
-        <v>4493</v>
-      </c>
-    </row>
-    <row r="4688" spans="3:4">
-      <c r="C4688" s="1"/>
-      <c r="D4688" t="s">
-        <v>4492</v>
-      </c>
-    </row>
-    <row r="4689" spans="2:4">
-      <c r="C4689" s="1"/>
-      <c r="D4689" t="s">
-        <v>4494</v>
-      </c>
-    </row>
-    <row r="4690" spans="2:4">
-      <c r="C4690" s="1"/>
-      <c r="D4690" t="s">
-        <v>4495</v>
-      </c>
-    </row>
-    <row r="4691" spans="2:4">
-      <c r="C4691" s="1" t="s">
+      <c r="C4684" s="1" t="s">
         <v>4496</v>
       </c>
     </row>
+    <row r="4685" spans="3:4" s="1" customFormat="1">
+      <c r="D4685" s="1" t="s">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="4686" spans="3:4" s="1" customFormat="1">
+      <c r="D4686" s="1" t="s">
+        <v>4498</v>
+      </c>
+    </row>
+    <row r="4687" spans="3:4" s="1" customFormat="1">
+      <c r="D4687" s="1" t="s">
+        <v>4499</v>
+      </c>
+    </row>
+    <row r="4688" spans="3:4" s="1" customFormat="1">
+      <c r="D4688" s="1" t="s">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="4689" spans="2:4" s="1" customFormat="1">
+      <c r="D4689" s="1" t="s">
+        <v>4501</v>
+      </c>
+    </row>
+    <row r="4690" spans="2:4" s="1" customFormat="1">
+      <c r="D4690" s="1" t="s">
+        <v>4502</v>
+      </c>
+    </row>
+    <row r="4691" spans="2:4" s="1" customFormat="1">
+      <c r="D4691" s="1" t="s">
+        <v>4531</v>
+      </c>
+    </row>
     <row r="4692" spans="2:4" s="1" customFormat="1">
-      <c r="D4692" s="1" t="s">
-        <v>4497</v>
+      <c r="D4692" s="3" t="s">
+        <v>4532</v>
       </c>
     </row>
     <row r="4693" spans="2:4" s="1" customFormat="1">
-      <c r="D4693" s="1" t="s">
-        <v>4498</v>
-      </c>
-    </row>
-    <row r="4694" spans="2:4" s="1" customFormat="1">
-      <c r="D4694" s="1" t="s">
-        <v>4499</v>
-      </c>
-    </row>
-    <row r="4695" spans="2:4" s="1" customFormat="1">
-      <c r="D4695" s="1" t="s">
-        <v>4500</v>
-      </c>
-    </row>
-    <row r="4696" spans="2:4" s="1" customFormat="1">
-      <c r="D4696" s="1" t="s">
-        <v>4501</v>
-      </c>
-    </row>
-    <row r="4697" spans="2:4" s="1" customFormat="1">
-      <c r="D4697" s="1" t="s">
-        <v>4502</v>
+      <c r="D4693" t="s">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="4694" spans="2:4">
+      <c r="B4694" t="s">
+        <v>4435</v>
+      </c>
+    </row>
+    <row r="4695" spans="2:4">
+      <c r="C4695" s="1" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="4696" spans="2:4">
+      <c r="C4696" s="1" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="4697" spans="2:4">
+      <c r="B4697" s="1"/>
+      <c r="C4697" s="1" t="s">
+        <v>4444</v>
       </c>
     </row>
     <row r="4698" spans="2:4">
-      <c r="B4698" t="s">
-        <v>4435</v>
+      <c r="B4698" s="1"/>
+      <c r="C4698" s="1" t="s">
+        <v>4445</v>
       </c>
     </row>
     <row r="4699" spans="2:4">
+      <c r="B4699" s="1"/>
       <c r="C4699" s="1" t="s">
-        <v>4436</v>
+        <v>4446</v>
       </c>
     </row>
     <row r="4700" spans="2:4">
       <c r="C4700" s="1" t="s">
-        <v>4440</v>
-      </c>
-    </row>
-    <row r="4701" spans="2:4">
-      <c r="B4701" s="1"/>
-      <c r="C4701" s="1" t="s">
-        <v>4444</v>
-      </c>
-    </row>
-    <row r="4702" spans="2:4">
-      <c r="B4702" s="1"/>
-      <c r="C4702" s="1" t="s">
-        <v>4445</v>
-      </c>
-    </row>
-    <row r="4703" spans="2:4">
-      <c r="B4703" s="1"/>
-      <c r="C4703" s="1" t="s">
-        <v>4446</v>
-      </c>
-    </row>
-    <row r="4704" spans="2:4">
-      <c r="C4704" s="1" t="s">
         <v>4448</v>
       </c>
     </row>

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF417339-4A86-4D50-8C16-BF3E12F93C53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CFD151-209B-48E8-AEAD-E569F795DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="new-simple-2026.R2" sheetId="3" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14108" uniqueCount="4546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14108" uniqueCount="4547">
   <si>
     <t>大正新脩大藏經</t>
   </si>
@@ -13908,6 +13908,10 @@
   <si>
     <t>JB277_017..018 JB277 (卷17-18) 雲棲法彙（選錄）山房雜錄</t>
     <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>T0262_007 T0262 (卷7) 妙法蓮華經（觀世音菩薩普門品）</t>
+    <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -26297,7 +26301,7 @@
     </row>
     <row r="2280" spans="2:5">
       <c r="E2280" t="s">
-        <v>2232</v>
+        <v>4546</v>
       </c>
     </row>
     <row r="2281" spans="2:5">
@@ -38497,6 +38501,7 @@
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CFD151-209B-48E8-AEAD-E569F795DD57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E80152-15A9-4884-9F7C-DB623AA01C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13910,7 +13910,7 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>T0262_007 T0262 (卷7) 妙法蓮華經（觀世音菩薩普門品）</t>
+    <t>T0262_007 T0262 (卷7) 妙法蓮華經〈觀世音菩薩普門品〉</t>
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>

--- a/cbreader2X/nav/simple_nav.xlsx
+++ b/cbreader2X/nav/simple_nav.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cbwork\bin\cbreader2X\nav\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E80152-15A9-4884-9F7C-DB623AA01C12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{692AA98F-E30A-410B-8EC0-6E8A4A576ABE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13910,7 +13910,7 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>T0262_007 T0262 (卷7) 妙法蓮華經〈觀世音菩薩普門品〉</t>
+    <t>T09n0262_p0056c02 T0262 (卷7) 妙法蓮華經觀世音菩薩普門品</t>
     <phoneticPr fontId="23" type="noConversion"/>
   </si>
 </sst>
